--- a/survey_templates/045_relationship_accountability_survey--survey_templates.xlsx
+++ b/survey_templates/045_relationship_accountability_survey--survey_templates.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -882,7 +882,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Both_me_and_my_partner</t>
+          <t>Both me and my partner</t>
         </is>
       </c>
     </row>
@@ -916,7 +916,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>My_partner</t>
+          <t>My partner</t>
         </is>
       </c>
     </row>
@@ -984,7 +984,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>My_partner</t>
+          <t>My partner</t>
         </is>
       </c>
     </row>
@@ -1137,7 +1137,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>In_a_relationship</t>
+          <t>In a relationship</t>
         </is>
       </c>
     </row>
@@ -1239,7 +1239,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Video_call</t>
+          <t>Video call</t>
         </is>
       </c>
     </row>
@@ -1256,7 +1256,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Social_media</t>
+          <t>Social media</t>
         </is>
       </c>
     </row>
@@ -1358,7 +1358,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Love_and_support</t>
+          <t>Love and support</t>
         </is>
       </c>
     </row>
@@ -1375,7 +1375,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Personal_growth</t>
+          <t>Personal growth</t>
         </is>
       </c>
     </row>
@@ -1392,7 +1392,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Shared_goals</t>
+          <t>Shared goals</t>
         </is>
       </c>
     </row>
